--- a/results/08-2025/beta/contributions-08-2025.xlsx
+++ b/results/08-2025/beta/contributions-08-2025.xlsx
@@ -20475,7 +20475,7 @@
         <v>-0.0153417435784926</v>
       </c>
       <c r="K204" t="n">
-        <v>1.60009342235307</v>
+        <v>1.2541664075143</v>
       </c>
       <c r="L204" t="n">
         <v>0.0106000086913442</v>
@@ -20526,16 +20526,16 @@
         <v>0.607898789078671</v>
       </c>
       <c r="AB204" t="n">
-        <v>5.40961284869081</v>
+        <v>5.07416455365338</v>
       </c>
       <c r="AC204" t="n">
-        <v>5.99171227481882</v>
+        <v>5.65787472424105</v>
       </c>
       <c r="AD204" t="n">
-        <v>4.39541334317949</v>
+        <v>4.06157579260172</v>
       </c>
       <c r="AE204" t="n">
-        <v>3.93521278138719</v>
+        <v>3.85175339374274</v>
       </c>
     </row>
     <row r="205">
@@ -20570,7 +20570,7 @@
         <v>-0.0130950138175455</v>
       </c>
       <c r="K205" t="n">
-        <v>0.599614860666462</v>
+        <v>0.451426424254091</v>
       </c>
       <c r="L205" t="n">
         <v>0.0182667195699809</v>
@@ -20621,16 +20621,16 @@
         <v>-0.572771043109975</v>
       </c>
       <c r="AB205" t="n">
-        <v>-2.2524780800358</v>
+        <v>-2.40508436218247</v>
       </c>
       <c r="AC205" t="n">
-        <v>-2.83862676595735</v>
+        <v>-2.99213568098258</v>
       </c>
       <c r="AD205" t="n">
-        <v>-3.48042894497274</v>
+        <v>-3.63393785999797</v>
       </c>
       <c r="AE205" t="n">
-        <v>2.93469077366695</v>
+        <v>2.8128541572662</v>
       </c>
     </row>
     <row r="206">
@@ -20665,7 +20665,7 @@
         <v>-0.00989953956522997</v>
       </c>
       <c r="K206" t="n">
-        <v>1.29043438211067</v>
+        <v>1.20173560179115</v>
       </c>
       <c r="L206" t="n">
         <v>0.00125001719121796</v>
@@ -20716,16 +20716,16 @@
         <v>-0.204262689318327</v>
       </c>
       <c r="AB206" t="n">
-        <v>7.95276650963092</v>
+        <v>7.87002625717231</v>
       </c>
       <c r="AC206" t="n">
-        <v>7.76463749740689</v>
+        <v>7.68172705910506</v>
       </c>
       <c r="AD206" t="n">
-        <v>8.43112996863139</v>
+        <v>8.34821953032956</v>
       </c>
       <c r="AE206" t="n">
-        <v>4.92557007914553</v>
+        <v>4.78300585316932</v>
       </c>
     </row>
     <row r="207">
@@ -20760,7 +20760,7 @@
         <v>-0.0107023247685096</v>
       </c>
       <c r="K207" t="n">
-        <v>-0.162243842200414</v>
+        <v>-0.212648567222338</v>
       </c>
       <c r="L207" t="n">
         <v>-0.00774681276657265</v>
@@ -20811,16 +20811,16 @@
         <v>-0.243455656681872</v>
       </c>
       <c r="AB207" t="n">
-        <v>-0.988452361025347</v>
+        <v>-1.03923792732915</v>
       </c>
       <c r="AC207" t="n">
-        <v>-1.234111874472</v>
+        <v>-1.28501049393692</v>
       </c>
       <c r="AD207" t="n">
-        <v>-2.37330244991499</v>
+        <v>-2.42420106937991</v>
       </c>
       <c r="AE207" t="n">
-        <v>1.74320297923079</v>
+        <v>1.58791409838835</v>
       </c>
     </row>
     <row r="208">
@@ -20855,7 +20855,7 @@
         <v>-0.0248545148755541</v>
       </c>
       <c r="K208" t="n">
-        <v>-0.25943860611616</v>
+        <v>-0.0861390825900978</v>
       </c>
       <c r="L208" t="n">
         <v>0.0111042146807673</v>
@@ -20906,16 +20906,16 @@
         <v>-0.329215322040202</v>
       </c>
       <c r="AB208" t="n">
-        <v>-2.21087661515167</v>
+        <v>-2.03420258223816</v>
       </c>
       <c r="AC208" t="n">
-        <v>-2.54737061062298</v>
+        <v>-2.37011687319389</v>
       </c>
       <c r="AD208" t="n">
-        <v>-3.17743573682826</v>
+        <v>-3.00018199939918</v>
       </c>
       <c r="AE208" t="n">
-        <v>-0.150009290771148</v>
+        <v>-0.177525349611874</v>
       </c>
     </row>
     <row r="209">
@@ -20950,7 +20950,7 @@
         <v>-0.0507473455174565</v>
       </c>
       <c r="K209" t="n">
-        <v>0.199759198319694</v>
+        <v>0.216925315885803</v>
       </c>
       <c r="L209" t="n">
         <v>0.00380906280060659</v>
@@ -21001,16 +21001,16 @@
         <v>-0.233915643603498</v>
       </c>
       <c r="AB209" t="n">
-        <v>-2.4082843016319</v>
+        <v>-2.39067872601153</v>
       </c>
       <c r="AC209" t="n">
-        <v>-2.64771465392573</v>
+        <v>-2.63006891806764</v>
       </c>
       <c r="AD209" t="n">
-        <v>-3.07135951951553</v>
+        <v>-3.05371378365743</v>
       </c>
       <c r="AE209" t="n">
-        <v>-0.0477419344068457</v>
+        <v>-0.0324693305267403</v>
       </c>
     </row>
     <row r="210">
@@ -21045,7 +21045,7 @@
         <v>-0.0422059225673767</v>
       </c>
       <c r="K210" t="n">
-        <v>-0.761030888584872</v>
+        <v>-0.774420589229686</v>
       </c>
       <c r="L210" t="n">
         <v>0.00141182685498095</v>
@@ -21096,16 +21096,16 @@
         <v>-0.887659949372401</v>
       </c>
       <c r="AB210" t="n">
-        <v>-2.0946499410967</v>
+        <v>-2.10821872916329</v>
       </c>
       <c r="AC210" t="n">
-        <v>-3.00109735153513</v>
+        <v>-3.01478741463564</v>
       </c>
       <c r="AD210" t="n">
-        <v>-3.95744707489977</v>
+        <v>-3.97113713800028</v>
       </c>
       <c r="AE210" t="n">
-        <v>-3.14488619528964</v>
+        <v>-3.1123084976092</v>
       </c>
     </row>
     <row r="211">
@@ -21140,7 +21140,7 @@
         <v>-0.0303902006099443</v>
       </c>
       <c r="K211" t="n">
-        <v>0.0491749025761899</v>
+        <v>0.0317769416054721</v>
       </c>
       <c r="L211" t="n">
         <v>0.0245007375899431</v>
@@ -21191,16 +21191,16 @@
         <v>-1.23221650839596</v>
       </c>
       <c r="AB211" t="n">
-        <v>-3.019121873259</v>
+        <v>-3.03705008623437</v>
       </c>
       <c r="AC211" t="n">
-        <v>-4.28819583008987</v>
+        <v>-4.30634183167421</v>
       </c>
       <c r="AD211" t="n">
-        <v>-4.93065167834356</v>
+        <v>-4.9487976799279</v>
       </c>
       <c r="AE211" t="n">
-        <v>-3.78422350239678</v>
+        <v>-3.7434576502462</v>
       </c>
     </row>
     <row r="212">
@@ -21235,7 +21235,7 @@
         <v>-0.0345732200981598</v>
       </c>
       <c r="K212" t="n">
-        <v>-0.490461568607645</v>
+        <v>-0.445412693504854</v>
       </c>
       <c r="L212" t="n">
         <v>0.0970174716180036</v>
@@ -21286,16 +21286,16 @@
         <v>-0.644554894533726</v>
       </c>
       <c r="AB212" t="n">
-        <v>-1.70596838526932</v>
+        <v>-1.66035827204886</v>
       </c>
       <c r="AC212" t="n">
-        <v>-2.36184671088028</v>
+        <v>-2.31593471289617</v>
       </c>
       <c r="AD212" t="n">
-        <v>-2.47519422497221</v>
+        <v>-2.42928222698809</v>
       </c>
       <c r="AE212" t="n">
-        <v>-3.60866312443276</v>
+        <v>-3.60073270714343</v>
       </c>
     </row>
     <row r="213">
@@ -21330,7 +21330,7 @@
         <v>-0.0377103170242398</v>
       </c>
       <c r="K213" t="n">
-        <v>-0.156314743350148</v>
+        <v>-0.0541728732261475</v>
       </c>
       <c r="L213" t="n">
         <v>0.284621349042765</v>
@@ -21381,16 +21381,16 @@
         <v>-0.413228508543044</v>
       </c>
       <c r="AB213" t="n">
-        <v>-0.466990551223606</v>
+        <v>-0.364517338822344</v>
       </c>
       <c r="AC213" t="n">
-        <v>-0.882236040055477</v>
+        <v>-0.779320516046776</v>
       </c>
       <c r="AD213" t="n">
-        <v>-0.333728106887537</v>
+        <v>-0.230812582878836</v>
       </c>
       <c r="AE213" t="n">
-        <v>-2.92425527127577</v>
+        <v>-2.89500740694878</v>
       </c>
     </row>
     <row r="214">
@@ -21425,7 +21425,7 @@
         <v>-0.0386821553317883</v>
       </c>
       <c r="K214" t="n">
-        <v>-0.225719994392193</v>
+        <v>-0.125589671929754</v>
       </c>
       <c r="L214" t="n">
         <v>0.0388350944057053</v>
@@ -21476,16 +21476,16 @@
         <v>0.682764491074174</v>
       </c>
       <c r="AB214" t="n">
-        <v>-1.29636419468729</v>
+        <v>-1.19515075972747</v>
       </c>
       <c r="AC214" t="n">
-        <v>-0.604624362808381</v>
+        <v>-0.504110279154896</v>
       </c>
       <c r="AD214" t="n">
-        <v>-0.119951773096812</v>
+        <v>-0.0194376894433263</v>
       </c>
       <c r="AE214" t="n">
-        <v>-1.96488144582503</v>
+        <v>-1.90708254480954</v>
       </c>
     </row>
     <row r="215">
@@ -21520,7 +21520,7 @@
         <v>-0.0387564790130729</v>
       </c>
       <c r="K215" t="n">
-        <v>-0.185020954545194</v>
+        <v>-0.115254071270035</v>
       </c>
       <c r="L215" t="n">
         <v>-0.0105778727488364</v>
@@ -21571,16 +21571,16 @@
         <v>0.593603251254018</v>
       </c>
       <c r="AB215" t="n">
-        <v>-1.38970736836722</v>
+        <v>-1.31905434262686</v>
       </c>
       <c r="AC215" t="n">
-        <v>-0.787378506325261</v>
+        <v>-0.717168075423947</v>
       </c>
       <c r="AD215" t="n">
-        <v>-0.671859348760294</v>
+        <v>-0.601648917858979</v>
       </c>
       <c r="AE215" t="n">
-        <v>-0.900183363429211</v>
+        <v>-0.820295354292309</v>
       </c>
     </row>
     <row r="216">
@@ -21615,7 +21615,7 @@
         <v>-0.0326613401835033</v>
       </c>
       <c r="K216" t="n">
-        <v>-0.0746942928304732</v>
+        <v>-0.0465255145967894</v>
       </c>
       <c r="L216" t="n">
         <v>-0.0761975820429207</v>
@@ -21666,16 +21666,16 @@
         <v>0.266647508851525</v>
       </c>
       <c r="AB216" t="n">
-        <v>-0.783450874876392</v>
+        <v>-0.755073656707563</v>
       </c>
       <c r="AC216" t="n">
-        <v>-0.514619418777226</v>
+        <v>-0.486321201641255</v>
       </c>
       <c r="AD216" t="n">
-        <v>0.0694638874198354</v>
+        <v>0.0977621045558065</v>
       </c>
       <c r="AE216" t="n">
-        <v>-0.264018835331201</v>
+        <v>-0.188534271406334</v>
       </c>
     </row>
     <row r="217">
@@ -21710,7 +21710,7 @@
         <v>-0.0336567575945296</v>
       </c>
       <c r="K217" t="n">
-        <v>-0.228585040072361</v>
+        <v>-0.212007006203846</v>
       </c>
       <c r="L217" t="n">
         <v>-0.244035955453352</v>
@@ -21761,16 +21761,16 @@
         <v>0.046268702022736</v>
       </c>
       <c r="AB217" t="n">
-        <v>-0.760809840097496</v>
+        <v>-0.744139242750871</v>
       </c>
       <c r="AC217" t="n">
-        <v>-0.714170785511845</v>
+        <v>-0.697508292678386</v>
       </c>
       <c r="AD217" t="n">
-        <v>-0.480060203643271</v>
+        <v>-0.463397710809811</v>
       </c>
       <c r="AE217" t="n">
-        <v>-0.300601859520134</v>
+        <v>-0.246680553389078</v>
       </c>
     </row>
     <row r="218">
@@ -21865,7 +21865,7 @@
         <v>-0.00519473947615287</v>
       </c>
       <c r="AE218" t="n">
-        <v>-0.271912601114969</v>
+        <v>-0.243119815897285</v>
       </c>
     </row>
     <row r="219">
@@ -21960,7 +21960,7 @@
         <v>0.120096195251555</v>
       </c>
       <c r="AE219" t="n">
-        <v>-0.0739237151120072</v>
+        <v>-0.062683537619651</v>
       </c>
     </row>
     <row r="220">
@@ -22055,7 +22055,7 @@
         <v>0.501432050050839</v>
       </c>
       <c r="AE220" t="n">
-        <v>0.0340683255457437</v>
+        <v>0.0382339487541071</v>
       </c>
     </row>
     <row r="221">
@@ -22150,7 +22150,7 @@
         <v>0.351693263923657</v>
       </c>
       <c r="AE221" t="n">
-        <v>0.242006692437476</v>
+        <v>0.242006692437474</v>
       </c>
     </row>
     <row r="222">
@@ -22245,7 +22245,7 @@
         <v>-0.513111879169799</v>
       </c>
       <c r="AE222" t="n">
-        <v>0.115027407514064</v>
+        <v>0.115027407514063</v>
       </c>
     </row>
     <row r="223">
@@ -22259,88 +22259,88 @@
         <v>-1</v>
       </c>
       <c r="D223" t="n">
-        <v>-0.391562387656813</v>
+        <v>-0.456494791403439</v>
       </c>
       <c r="E223" t="n">
-        <v>0.0781528904100504</v>
+        <v>0.0332796849161851</v>
       </c>
       <c r="F223" t="n">
-        <v>-0.423915636094668</v>
+        <v>-0.430852894750782</v>
       </c>
       <c r="G223" t="n">
-        <v>-0.0589586562014646</v>
+        <v>-0.0705832073265445</v>
       </c>
       <c r="H223" t="n">
-        <v>0.217536719389177</v>
+        <v>0.217193575061216</v>
       </c>
       <c r="I223" t="n">
-        <v>0.186318851219056</v>
+        <v>0.186577440159198</v>
       </c>
       <c r="J223" t="n">
-        <v>0.0817396190303596</v>
+        <v>0.0816178148014952</v>
       </c>
       <c r="K223" t="n">
-        <v>0.374980570389029</v>
+        <v>0.386595939179431</v>
       </c>
       <c r="L223" t="n">
-        <v>-0.00852330729001726</v>
+        <v>-0.00743983081949417</v>
       </c>
       <c r="M223" t="n">
         <v>0</v>
       </c>
       <c r="N223" t="n">
-        <v>-0.0944410633449994</v>
+        <v>-0.0944653554178668</v>
       </c>
       <c r="O223" t="n">
         <v>0</v>
       </c>
       <c r="P223" t="n">
-        <v>0.0007240886257028</v>
+        <v>0.000801713950782644</v>
       </c>
       <c r="Q223" t="n">
-        <v>-0.0939392772317754</v>
+        <v>-0.0938335784893964</v>
       </c>
       <c r="R223" t="n">
-        <v>-0.0265892738036949</v>
+        <v>-0.0265897358016603</v>
       </c>
       <c r="S223" t="n">
-        <v>-0.0134023793177287</v>
+        <v>-0.0133939093799328</v>
       </c>
       <c r="T223" t="n">
-        <v>-0.00996159982828873</v>
+        <v>-0.00995667921093501</v>
       </c>
       <c r="U223" t="n">
-        <v>-0.0236069317052464</v>
+        <v>-0.0236075413068481</v>
       </c>
       <c r="V223" t="n">
-        <v>-0.00103193276551185</v>
+        <v>-0.00103145556754683</v>
       </c>
       <c r="W223" t="n">
-        <v>0.281367873778438</v>
+        <v>0.285260329516038</v>
       </c>
       <c r="X223" t="n">
-        <v>-0.021653933348015</v>
+        <v>-0.0170103152405039</v>
       </c>
       <c r="Y223" t="n">
-        <v>-0.831205203287137</v>
+        <v>-0.901128628201745</v>
       </c>
       <c r="Z223" t="n">
-        <v>0.517795706040374</v>
+        <v>0.47791352171449</v>
       </c>
       <c r="AA223" t="n">
-        <v>0.00416006564299416</v>
+        <v>-0.0145711229004526</v>
       </c>
       <c r="AB223" t="n">
-        <v>0.364490028612786</v>
+        <v>0.385868741180201</v>
       </c>
       <c r="AC223" t="n">
-        <v>0.0686340024175949</v>
+        <v>0.0713572533757167</v>
       </c>
       <c r="AD223" t="n">
-        <v>-0.244775494829168</v>
+        <v>-0.351857853111538</v>
       </c>
       <c r="AE223" t="n">
-        <v>0.0238094849938834</v>
+        <v>-0.00296110457671061</v>
       </c>
     </row>
     <row r="224">
@@ -22354,88 +22354,88 @@
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.0291015472775402</v>
+        <v>0.0290736881361319</v>
       </c>
       <c r="E224" t="n">
-        <v>-0.188207035970589</v>
+        <v>-0.188048311746175</v>
       </c>
       <c r="F224" t="n">
-        <v>-0.28448146421088</v>
+        <v>-0.274584799806063</v>
       </c>
       <c r="G224" t="n">
-        <v>-0.0246809389958226</v>
+        <v>-0.0270800925481991</v>
       </c>
       <c r="H224" t="n">
-        <v>0.145262780558903</v>
+        <v>0.144757848511787</v>
       </c>
       <c r="I224" t="n">
-        <v>0.185359698888098</v>
+        <v>0.184897094298286</v>
       </c>
       <c r="J224" t="n">
-        <v>0.00351457865919616</v>
+        <v>0.00977651845857025</v>
       </c>
       <c r="K224" t="n">
-        <v>0.314442373113224</v>
+        <v>0.252578609888955</v>
       </c>
       <c r="L224" t="n">
-        <v>0.00894725752390453</v>
+        <v>0.00821013245080898</v>
       </c>
       <c r="M224" t="n">
         <v>0</v>
       </c>
       <c r="N224" t="n">
-        <v>-0.000998172134519155</v>
+        <v>-0.000998203190626981</v>
       </c>
       <c r="O224" t="n">
         <v>0</v>
       </c>
       <c r="P224" t="n">
-        <v>-0.00460271895022645</v>
+        <v>-0.00471875785945323</v>
       </c>
       <c r="Q224" t="n">
-        <v>-0.0729284242867051</v>
+        <v>-0.073074762283519</v>
       </c>
       <c r="R224" t="n">
-        <v>-0.0261051959502162</v>
+        <v>-0.0260956522140968</v>
       </c>
       <c r="S224" t="n">
-        <v>-0.0137414297319154</v>
+        <v>-0.0137496111357103</v>
       </c>
       <c r="T224" t="n">
-        <v>-0.00849828342381878</v>
+        <v>-0.00850353127622489</v>
       </c>
       <c r="U224" t="n">
-        <v>-0.0297244343570672</v>
+        <v>-0.0297107360037447</v>
       </c>
       <c r="V224" t="n">
-        <v>-0.000520541582908059</v>
+        <v>-0.000521305315914501</v>
       </c>
       <c r="W224" t="n">
-        <v>0.2121781891664</v>
+        <v>0.250783080665764</v>
       </c>
       <c r="X224" t="n">
-        <v>0.0232516749060726</v>
+        <v>0.0241637683714257</v>
       </c>
       <c r="Y224" t="n">
-        <v>-0.0229827206853852</v>
+        <v>-0.0229714599456522</v>
       </c>
       <c r="Z224" t="n">
-        <v>-0.136122768007664</v>
+        <v>-0.136003163664391</v>
       </c>
       <c r="AA224" t="n">
-        <v>0.0256963569760872</v>
+        <v>0.038454553553038</v>
       </c>
       <c r="AB224" t="n">
-        <v>0.401648149945798</v>
+        <v>0.378316475024545</v>
       </c>
       <c r="AC224" t="n">
-        <v>0.127235077838726</v>
+        <v>0.116616690285533</v>
       </c>
       <c r="AD224" t="n">
-        <v>-0.031870410854323</v>
+        <v>-0.0423579333245097</v>
       </c>
       <c r="AE224" t="n">
-        <v>-0.109516130232407</v>
+        <v>-0.138908600420548</v>
       </c>
     </row>
     <row r="225">
@@ -22449,88 +22449,88 @@
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>-0.147415260686794</v>
+        <v>-0.471839595461538</v>
       </c>
       <c r="E225" t="n">
-        <v>-0.187231984668563</v>
+        <v>-0.187074082752734</v>
       </c>
       <c r="F225" t="n">
-        <v>-0.193197673751037</v>
+        <v>-0.174895622029105</v>
       </c>
       <c r="G225" t="n">
-        <v>-0.0138590061138467</v>
+        <v>-0.00772929224622736</v>
       </c>
       <c r="H225" t="n">
-        <v>0.0307276148291852</v>
+        <v>0.0307738989004688</v>
       </c>
       <c r="I225" t="n">
-        <v>0.0721388183794355</v>
+        <v>0.0714060553188929</v>
       </c>
       <c r="J225" t="n">
-        <v>0.00498265591511215</v>
+        <v>0.0112796004350919</v>
       </c>
       <c r="K225" t="n">
-        <v>0.22585716259006</v>
+        <v>0.159087657012174</v>
       </c>
       <c r="L225" t="n">
-        <v>0.0305012797511961</v>
+        <v>0.0291523129870315</v>
       </c>
       <c r="M225" t="n">
         <v>0</v>
       </c>
       <c r="N225" t="n">
-        <v>-0.000975940925236092</v>
+        <v>-0.000976143340924566</v>
       </c>
       <c r="O225" t="n">
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>-0.00526220081185437</v>
+        <v>-0.00547326792706527</v>
       </c>
       <c r="Q225" t="n">
-        <v>-0.0356074781047652</v>
+        <v>-0.0359108681157127</v>
       </c>
       <c r="R225" t="n">
-        <v>-0.00391689079893773</v>
+        <v>-0.00391958462275576</v>
       </c>
       <c r="S225" t="n">
-        <v>-0.0128933818456295</v>
+        <v>-0.0129106719232023</v>
       </c>
       <c r="T225" t="n">
-        <v>-0.0076975622841696</v>
+        <v>-0.00770880481661571</v>
       </c>
       <c r="U225" t="n">
-        <v>-0.0246723690474352</v>
+        <v>-0.0246551070924505</v>
       </c>
       <c r="V225" t="n">
-        <v>-0.000445890310880037</v>
+        <v>-0.000447402296452819</v>
       </c>
       <c r="W225" t="n">
-        <v>0.15990612829068</v>
+        <v>0.214937475824796</v>
       </c>
       <c r="X225" t="n">
-        <v>0.0405795583280417</v>
+        <v>0.0409192022073464</v>
       </c>
       <c r="Y225" t="n">
-        <v>-0.251753485381384</v>
+        <v>-0.576099473667565</v>
       </c>
       <c r="Z225" t="n">
-        <v>-0.0828937599739729</v>
+        <v>-0.0828142045467079</v>
       </c>
       <c r="AA225" t="n">
-        <v>-0.0990280287837447</v>
+        <v>-0.0689953159126711</v>
       </c>
       <c r="AB225" t="n">
-        <v>0.365095059937961</v>
+        <v>0.351840785318743</v>
       </c>
       <c r="AC225" t="n">
-        <v>-0.0335490520877683</v>
+        <v>-0.0168965928346227</v>
       </c>
       <c r="AD225" t="n">
-        <v>-0.368196297443125</v>
+        <v>-0.675810271048896</v>
       </c>
       <c r="AE225" t="n">
-        <v>-0.289488520574103</v>
+        <v>-0.395784484163686</v>
       </c>
     </row>
     <row r="226">
@@ -22544,88 +22544,88 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.18276212819498</v>
+        <v>0.0511746801573396</v>
       </c>
       <c r="E226" t="n">
-        <v>-0.186051389811214</v>
+        <v>-0.185894483548933</v>
       </c>
       <c r="F226" t="n">
-        <v>-0.124853598459061</v>
+        <v>-0.115541650507629</v>
       </c>
       <c r="G226" t="n">
-        <v>-0.0302352091264087</v>
+        <v>-0.0290483876453611</v>
       </c>
       <c r="H226" t="n">
-        <v>0.0420773171393092</v>
+        <v>0.0416092966845123</v>
       </c>
       <c r="I226" t="n">
-        <v>0.315835073308651</v>
+        <v>0.315241515181555</v>
       </c>
       <c r="J226" t="n">
-        <v>0.00279733949862842</v>
+        <v>0.00876909394816765</v>
       </c>
       <c r="K226" t="n">
-        <v>0.119957971224332</v>
+        <v>0.0597848041545525</v>
       </c>
       <c r="L226" t="n">
-        <v>0.0389192434923418</v>
+        <v>0.038215567542527</v>
       </c>
       <c r="M226" t="n">
         <v>0</v>
       </c>
       <c r="N226" t="n">
-        <v>-0.000952435173347631</v>
+        <v>-0.000951951298125349</v>
       </c>
       <c r="O226" t="n">
         <v>0</v>
       </c>
       <c r="P226" t="n">
-        <v>-0.00465781480912921</v>
+        <v>-0.0047607164002074</v>
       </c>
       <c r="Q226" t="n">
-        <v>-0.00397491792910585</v>
+        <v>-0.00412856070754238</v>
       </c>
       <c r="R226" t="n">
-        <v>-0.00267939932142978</v>
+        <v>-0.00267925813630648</v>
       </c>
       <c r="S226" t="n">
-        <v>-0.0143573049569729</v>
+        <v>-0.0143568988034681</v>
       </c>
       <c r="T226" t="n">
-        <v>-0.00707107020008399</v>
+        <v>-0.00707241549523366</v>
       </c>
       <c r="U226" t="n">
-        <v>-0.0229254872932519</v>
+        <v>-0.0229029124821011</v>
       </c>
       <c r="V226" t="n">
-        <v>-0.00041272833968232</v>
+        <v>-0.000413234974622097</v>
       </c>
       <c r="W226" t="n">
-        <v>0.176361284115549</v>
+        <v>0.25800282211999</v>
       </c>
       <c r="X226" t="n">
-        <v>-0.00263935170918194</v>
+        <v>-0.00106525379914117</v>
       </c>
       <c r="Y226" t="n">
-        <v>0.131365421185271</v>
+        <v>-0.000183423426840579</v>
       </c>
       <c r="Z226" t="n">
-        <v>-0.134654682801505</v>
+        <v>-0.134536379964753</v>
       </c>
       <c r="AA226" t="n">
-        <v>0.206024476956956</v>
+        <v>0.221384449494031</v>
       </c>
       <c r="AB226" t="n">
-        <v>0.275418168268284</v>
+        <v>0.297585637717893</v>
       </c>
       <c r="AC226" t="n">
-        <v>0.18083761874536</v>
+        <v>0.218267153279602</v>
       </c>
       <c r="AD226" t="n">
-        <v>0.177548357129126</v>
+        <v>0.0835473498880084</v>
       </c>
       <c r="AE226" t="n">
-        <v>-0.116823461499371</v>
+        <v>-0.246619676899234</v>
       </c>
     </row>
     <row r="227">
@@ -22639,31 +22639,31 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>-0.0914989396674436</v>
+        <v>-0.0206345152261397</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.197098769893092</v>
+        <v>-0.196932546833348</v>
       </c>
       <c r="F227" t="n">
-        <v>-0.111831377165716</v>
+        <v>-0.102466074612159</v>
       </c>
       <c r="G227" t="n">
-        <v>-0.0185363518653894</v>
+        <v>-0.0172999008040784</v>
       </c>
       <c r="H227" t="n">
-        <v>0.0397911929794883</v>
+        <v>0.0393401761663312</v>
       </c>
       <c r="I227" t="n">
-        <v>0.250538044168492</v>
+        <v>0.249914899391776</v>
       </c>
       <c r="J227" t="n">
-        <v>0.00405859116102814</v>
+        <v>0.00993493035255566</v>
       </c>
       <c r="K227" t="n">
-        <v>-0.0964496209567767</v>
+        <v>-0.162194189612503</v>
       </c>
       <c r="L227" t="n">
-        <v>0.0483076284777866</v>
+        <v>0.0469935548593457</v>
       </c>
       <c r="M227" t="n">
         <v>0</v>
@@ -22675,52 +22675,52 @@
         <v>0</v>
       </c>
       <c r="P227" t="n">
-        <v>-0.00501229776042769</v>
+        <v>-0.00511420223563733</v>
       </c>
       <c r="Q227" t="n">
-        <v>-0.00123929059572625</v>
+        <v>-0.00139461046029469</v>
       </c>
       <c r="R227" t="n">
-        <v>-0.00225012454482906</v>
+        <v>-0.00224965908214383</v>
       </c>
       <c r="S227" t="n">
-        <v>-0.00987872867142038</v>
+        <v>-0.00987822204307324</v>
       </c>
       <c r="T227" t="n">
-        <v>-0.00649350946650114</v>
+        <v>-0.00649358834770206</v>
       </c>
       <c r="U227" t="n">
-        <v>-0.0210948866777623</v>
+        <v>-0.0210680717122167</v>
       </c>
       <c r="V227" t="n">
-        <v>-0.000383695634204903</v>
+        <v>-0.000384126472009933</v>
       </c>
       <c r="W227" t="n">
-        <v>0.0759890946654891</v>
+        <v>0.179479781049794</v>
       </c>
       <c r="X227" t="n">
-        <v>0.0281761613382162</v>
+        <v>0.0262335005039628</v>
       </c>
       <c r="Y227" t="n">
-        <v>-0.175711028259567</v>
+        <v>-0.104783362510174</v>
       </c>
       <c r="Z227" t="n">
-        <v>-0.112886681300968</v>
+        <v>-0.112783699549314</v>
       </c>
       <c r="AA227" t="n">
-        <v>0.164287776318198</v>
+        <v>0.179651355203077</v>
       </c>
       <c r="AB227" t="n">
-        <v>0.00977034355799154</v>
+        <v>0.0442500560019448</v>
       </c>
       <c r="AC227" t="n">
-        <v>-0.0259589655707904</v>
+        <v>0.023816735794926</v>
       </c>
       <c r="AD227" t="n">
-        <v>-0.314556675131326</v>
+        <v>-0.193750326264562</v>
       </c>
       <c r="AE227" t="n">
-        <v>-0.134268756574911</v>
+        <v>-0.20709279518749</v>
       </c>
     </row>
     <row r="228">
@@ -22734,31 +22734,31 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>-0.0713914092546146</v>
+        <v>-0.0669010828661762</v>
       </c>
       <c r="E228" t="n">
-        <v>-0.186925340169462</v>
+        <v>-0.18676769686198</v>
       </c>
       <c r="F228" t="n">
-        <v>-0.133711890385013</v>
+        <v>-0.124404689867857</v>
       </c>
       <c r="G228" t="n">
-        <v>-0.0043181761913685</v>
+        <v>-0.00303914547611883</v>
       </c>
       <c r="H228" t="n">
-        <v>0.0497382359617767</v>
+        <v>0.0492971994825275</v>
       </c>
       <c r="I228" t="n">
-        <v>0.0774405162859638</v>
+        <v>0.076886835372163</v>
       </c>
       <c r="J228" t="n">
-        <v>0.00559558692157512</v>
+        <v>0.0113264543454398</v>
       </c>
       <c r="K228" t="n">
-        <v>-0.066201433696298</v>
+        <v>-0.0720145498604004</v>
       </c>
       <c r="L228" t="n">
-        <v>0.0111955567825106</v>
+        <v>0.0104972167942346</v>
       </c>
       <c r="M228" t="n">
         <v>0</v>
@@ -22770,52 +22770,52 @@
         <v>0</v>
       </c>
       <c r="P228" t="n">
-        <v>-0.00507216806458537</v>
+        <v>-0.0051725357804013</v>
       </c>
       <c r="Q228" t="n">
-        <v>-0.000459949846609852</v>
+        <v>-0.00061514608679288</v>
       </c>
       <c r="R228" t="n">
-        <v>-0.00283945709569163</v>
+        <v>-0.00283799958228407</v>
       </c>
       <c r="S228" t="n">
-        <v>-0.00673671657610257</v>
+        <v>-0.00673615387335766</v>
       </c>
       <c r="T228" t="n">
-        <v>-0.0057923099332822</v>
+        <v>-0.0057913263248774</v>
       </c>
       <c r="U228" t="n">
-        <v>-0.0191280140611447</v>
+        <v>-0.0190975843736354</v>
       </c>
       <c r="V228" t="n">
-        <v>-0.000333844436854403</v>
+        <v>-0.000334217710096717</v>
       </c>
       <c r="W228" t="n">
-        <v>0.0910284558715304</v>
+        <v>0.173612471392396</v>
       </c>
       <c r="X228" t="n">
-        <v>0.0142159535339324</v>
+        <v>0.0140086231605196</v>
       </c>
       <c r="Y228" t="n">
-        <v>-0.105034412883283</v>
+        <v>-0.1005188161385</v>
       </c>
       <c r="Z228" t="n">
-        <v>-0.153282336540794</v>
+        <v>-0.153149963589656</v>
       </c>
       <c r="AA228" t="n">
-        <v>-0.00511473222964723</v>
+        <v>0.0101942577488389</v>
       </c>
       <c r="AB228" t="n">
-        <v>0.00994764383847354</v>
+        <v>0.0856729891929739</v>
       </c>
       <c r="AC228" t="n">
-        <v>-0.195166544065889</v>
+        <v>-0.104142103855633</v>
       </c>
       <c r="AD228" t="n">
-        <v>-0.453483293489966</v>
+        <v>-0.357810883583789</v>
       </c>
       <c r="AE228" t="n">
-        <v>-0.239671977233822</v>
+        <v>-0.28595603275231</v>
       </c>
     </row>
     <row r="229">
@@ -22829,31 +22829,31 @@
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>-0.165695315902942</v>
+        <v>-0.161141624137415</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.197694067301406</v>
+        <v>-0.19752734219816</v>
       </c>
       <c r="F229" t="n">
-        <v>-0.101365325995295</v>
+        <v>-0.0920144857987395</v>
       </c>
       <c r="G229" t="n">
-        <v>0.0110463487191915</v>
+        <v>0.012366870034935</v>
       </c>
       <c r="H229" t="n">
-        <v>0.055669138497308</v>
+        <v>0.0552353291999718</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.052973428563513</v>
+        <v>-0.0534508229996155</v>
       </c>
       <c r="J229" t="n">
-        <v>0.00591935690801142</v>
+        <v>0.0115588855036247</v>
       </c>
       <c r="K229" t="n">
-        <v>-0.0180679238248527</v>
+        <v>-0.0239217480335747</v>
       </c>
       <c r="L229" t="n">
-        <v>0.0113297269904241</v>
+        <v>0.0106257225647084</v>
       </c>
       <c r="M229" t="n">
         <v>0</v>
@@ -22865,52 +22865,52 @@
         <v>0</v>
       </c>
       <c r="P229" t="n">
-        <v>-0.00467883109052618</v>
+        <v>-0.00477868126254695</v>
       </c>
       <c r="Q229" t="n">
-        <v>0.0012426761551968</v>
+        <v>0.00108567858882338</v>
       </c>
       <c r="R229" t="n">
-        <v>-0.000298818950572954</v>
+        <v>-0.000298578629093907</v>
       </c>
       <c r="S229" t="n">
-        <v>-0.00307808736574553</v>
+        <v>-0.00307864468601216</v>
       </c>
       <c r="T229" t="n">
-        <v>-0.00321965592940295</v>
+        <v>-0.00321920286264076</v>
       </c>
       <c r="U229" t="n">
-        <v>-0.0121080149151937</v>
+        <v>-0.0120781188734447</v>
       </c>
       <c r="V229" t="n">
-        <v>-0.000328437891201737</v>
+        <v>-0.000328736194169104</v>
       </c>
       <c r="W229" t="n">
-        <v>0.0574548369395306</v>
+        <v>0.118982886124508</v>
       </c>
       <c r="X229" t="n">
-        <v>-0.00183318436536394</v>
+        <v>-0.00224064950079607</v>
       </c>
       <c r="Y229" t="n">
-        <v>-0.224309758947194</v>
+        <v>-0.219712043659039</v>
       </c>
       <c r="Z229" t="n">
-        <v>-0.139079624257154</v>
+        <v>-0.138956922676536</v>
       </c>
       <c r="AA229" t="n">
-        <v>-0.0816523327738605</v>
+        <v>-0.0662494006814402</v>
       </c>
       <c r="AB229" t="n">
-        <v>0.0264316382478804</v>
+        <v>0.0807954091556325</v>
       </c>
       <c r="AC229" t="n">
-        <v>-0.255197664986214</v>
+        <v>-0.185396833349806</v>
       </c>
       <c r="AD229" t="n">
-        <v>-0.618587048190562</v>
+        <v>-0.544065799685382</v>
       </c>
       <c r="AE229" t="n">
-        <v>-0.302269664920681</v>
+        <v>-0.253019914911432</v>
       </c>
     </row>
     <row r="230">
@@ -22924,31 +22924,31 @@
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>-0.162823637322638</v>
+        <v>-0.158466821334579</v>
       </c>
       <c r="E230" t="n">
-        <v>-0.201907678509023</v>
+        <v>-0.201737399860781</v>
       </c>
       <c r="F230" t="n">
-        <v>-0.208494405668798</v>
+        <v>-0.208412240824727</v>
       </c>
       <c r="G230" t="n">
-        <v>0.0119546139133029</v>
+        <v>0.00827149761285744</v>
       </c>
       <c r="H230" t="n">
-        <v>0.0493810541992499</v>
+        <v>0.0484814463667788</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.20126968450116</v>
+        <v>-0.201118471675649</v>
       </c>
       <c r="J230" t="n">
-        <v>0.00747498910597346</v>
+        <v>0.0128113031939363</v>
       </c>
       <c r="K230" t="n">
-        <v>-0.00974549636439345</v>
+        <v>-0.00882684282750332</v>
       </c>
       <c r="L230" t="n">
-        <v>0.0116207642944175</v>
+        <v>0.0116120355889339</v>
       </c>
       <c r="M230" t="n">
         <v>0</v>
@@ -22960,52 +22960,52 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>-0.00200871387649046</v>
+        <v>-0.00200720504985976</v>
       </c>
       <c r="Q230" t="n">
-        <v>0.00185701407274331</v>
+        <v>0.00185561919958703</v>
       </c>
       <c r="R230" t="n">
-        <v>-0.000293355636933606</v>
+        <v>-0.000293135285973008</v>
       </c>
       <c r="S230" t="n">
-        <v>-0.00137435279977466</v>
+        <v>-0.00137332046819237</v>
       </c>
       <c r="T230" t="n">
-        <v>-0.00182054635875799</v>
+        <v>-0.00181917887266478</v>
       </c>
       <c r="U230" t="n">
-        <v>-0.0115490525077617</v>
+        <v>-0.0115403774600901</v>
       </c>
       <c r="V230" t="n">
-        <v>-0.000322515093892632</v>
+        <v>-0.000322272840057639</v>
       </c>
       <c r="W230" t="n">
-        <v>0.0663193428782925</v>
+        <v>0.112229898668183</v>
       </c>
       <c r="X230" t="n">
-        <v>-0.00524459066796074</v>
+        <v>-0.00498191535034271</v>
       </c>
       <c r="Y230" t="n">
-        <v>-0.207360846589146</v>
+        <v>-0.202970578082751</v>
       </c>
       <c r="Z230" t="n">
-        <v>-0.157370469242515</v>
+        <v>-0.157233643112609</v>
       </c>
       <c r="AA230" t="n">
-        <v>-0.341110887762956</v>
+        <v>-0.340121231391124</v>
       </c>
       <c r="AB230" t="n">
-        <v>0.0474520937058321</v>
+        <v>0.0945548599513782</v>
       </c>
       <c r="AC230" t="n">
-        <v>-0.39348640801367</v>
+        <v>-0.345223628114209</v>
       </c>
       <c r="AD230" t="n">
-        <v>-0.75821772384533</v>
+        <v>-0.70542784930957</v>
       </c>
       <c r="AE230" t="n">
-        <v>-0.536211185164295</v>
+        <v>-0.450263714710826</v>
       </c>
     </row>
     <row r="231">
@@ -23019,31 +23019,31 @@
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>-0.140907683756577</v>
+        <v>-0.136650570787518</v>
       </c>
       <c r="E231" t="n">
-        <v>-0.190425237576237</v>
+        <v>-0.190264642633613</v>
       </c>
       <c r="F231" t="n">
-        <v>-0.0449755394677347</v>
+        <v>-0.0448629357513134</v>
       </c>
       <c r="G231" t="n">
-        <v>0.0200104973840823</v>
+        <v>0.0200895003945094</v>
       </c>
       <c r="H231" t="n">
-        <v>0.0634489810496287</v>
+        <v>0.0625645504775943</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.3127409257165</v>
+        <v>-0.312505937927771</v>
       </c>
       <c r="J231" t="n">
-        <v>0.00490226587861304</v>
+        <v>0.0100961466960383</v>
       </c>
       <c r="K231" t="n">
-        <v>-0.00539983987231659</v>
+        <v>-0.00449800049258956</v>
       </c>
       <c r="L231" t="n">
-        <v>0.0118544741668678</v>
+        <v>0.0118455699174571</v>
       </c>
       <c r="M231" t="n">
         <v>0</v>
@@ -23055,52 +23055,52 @@
         <v>0</v>
       </c>
       <c r="P231" t="n">
-        <v>-0.000156500953837483</v>
+        <v>-0.00015638339984809</v>
       </c>
       <c r="Q231" t="n">
-        <v>0.00150745580400287</v>
+        <v>0.00150632349686718</v>
       </c>
       <c r="R231" t="n">
-        <v>-0.000286612003097306</v>
+        <v>-0.00028639671753356</v>
       </c>
       <c r="S231" t="n">
-        <v>-0.00103731611021143</v>
+        <v>-0.00103653694070003</v>
       </c>
       <c r="T231" t="n">
-        <v>-0.0015311108367649</v>
+        <v>-0.00152996075777142</v>
       </c>
       <c r="U231" t="n">
-        <v>-0.00956113583778143</v>
+        <v>-0.00955395402409124</v>
       </c>
       <c r="V231" t="n">
-        <v>-0.000315181928034319</v>
+        <v>-0.000314945182438865</v>
       </c>
       <c r="W231" t="n">
-        <v>0.0639814185095286</v>
+        <v>0.0883835878734423</v>
       </c>
       <c r="X231" t="n">
-        <v>0.00223218222181615</v>
+        <v>0.00214890828553672</v>
       </c>
       <c r="Y231" t="n">
-        <v>-0.184532529701216</v>
+        <v>-0.180242649636723</v>
       </c>
       <c r="Z231" t="n">
-        <v>-0.146800391631598</v>
+        <v>-0.146672563784407</v>
       </c>
       <c r="AA231" t="n">
-        <v>-0.269184928564189</v>
+        <v>-0.264436258666976</v>
       </c>
       <c r="AB231" t="n">
-        <v>0.0612910936078365</v>
+        <v>0.086511372016813</v>
       </c>
       <c r="AC231" t="n">
-        <v>-0.307717320548898</v>
+        <v>-0.277679973204208</v>
       </c>
       <c r="AD231" t="n">
-        <v>-0.639050241881713</v>
+        <v>-0.604595186625339</v>
       </c>
       <c r="AE231" t="n">
-        <v>-0.617334576851892</v>
+        <v>-0.55297492980102</v>
       </c>
     </row>
     <row r="232">
@@ -23114,31 +23114,31 @@
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>-6.48061066878841</v>
+        <v>-6.37945551566077</v>
       </c>
       <c r="E232" t="n">
-        <v>-10.8986278041055</v>
+        <v>-10.8894364567339</v>
       </c>
       <c r="F232" t="n">
-        <v>7.67762368726203</v>
+        <v>7.67212622136009</v>
       </c>
       <c r="G232" t="n">
-        <v>4.15575500555642</v>
+        <v>4.16024531971358</v>
       </c>
       <c r="H232" t="n">
-        <v>0.224742111822221</v>
+        <v>0.224649461757912</v>
       </c>
       <c r="I232" t="n">
-        <v>-1.57354468312711</v>
+        <v>-1.57236082403902</v>
       </c>
       <c r="J232" t="n">
-        <v>0.0760479325580349</v>
+        <v>0.0755268981268547</v>
       </c>
       <c r="K232" t="n">
-        <v>-7.44272261744311</v>
+        <v>-7.37934505588072</v>
       </c>
       <c r="L232" t="n">
-        <v>-0.733943783378817</v>
+        <v>-0.733392072338369</v>
       </c>
       <c r="M232" t="n">
         <v>0</v>
@@ -23150,52 +23150,52 @@
         <v>0</v>
       </c>
       <c r="P232" t="n">
-        <v>-0.0946835715297874</v>
+        <v>-0.0946124440309528</v>
       </c>
       <c r="Q232" t="n">
-        <v>-0.0727083619463073</v>
+        <v>-0.0726537437450243</v>
       </c>
       <c r="R232" t="n">
-        <v>-0.000280986029323721</v>
+        <v>-0.000280774969690156</v>
       </c>
       <c r="S232" t="n">
-        <v>-0.00102139571406392</v>
+        <v>-0.00102062850298239</v>
       </c>
       <c r="T232" t="n">
-        <v>-0.00126560991298953</v>
+        <v>-0.00126465926268708</v>
       </c>
       <c r="U232" t="n">
-        <v>0.0257296506286633</v>
+        <v>0.0257103245980863</v>
       </c>
       <c r="V232" t="n">
-        <v>-0.000249918093292196</v>
+        <v>-0.000249730369945393</v>
       </c>
       <c r="W232" t="n">
-        <v>-6.0560894156482</v>
+        <v>-6.19545393079528</v>
       </c>
       <c r="X232" t="n">
-        <v>-0.977688018024556</v>
+        <v>-0.979700901584791</v>
       </c>
       <c r="Y232" t="n">
-        <v>-8.01277043535423</v>
+        <v>-7.91046441717539</v>
       </c>
       <c r="Z232" t="n">
-        <v>-9.36646803753971</v>
+        <v>-9.3584275552193</v>
       </c>
       <c r="AA232" t="n">
-        <v>10.3752838690418</v>
+        <v>10.3745034598958</v>
       </c>
       <c r="AB232" t="n">
-        <v>-16.1088882869701</v>
+        <v>-16.1951498741797</v>
       </c>
       <c r="AC232" t="n">
-        <v>-3.95381115939138</v>
+        <v>-4.03060613321881</v>
       </c>
       <c r="AD232" t="n">
-        <v>-21.3330496322853</v>
+        <v>-21.2994981056135</v>
       </c>
       <c r="AE232" t="n">
-        <v>-5.83722616155073</v>
+        <v>-5.78839673530845</v>
       </c>
     </row>
     <row r="233">
@@ -23215,25 +23215,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F233" t="n">
-        <v>7.62915874462344</v>
+        <v>7.62369462215413</v>
       </c>
       <c r="G233" t="n">
-        <v>4.12139391083715</v>
+        <v>4.12584459469924</v>
       </c>
       <c r="H233" t="n">
-        <v>0.228704907457406</v>
+        <v>0.228608360460185</v>
       </c>
       <c r="I233" t="n">
         <v>0</v>
       </c>
       <c r="J233" t="n">
-        <v>0.0754021107266993</v>
+        <v>0.0748871564802584</v>
       </c>
       <c r="K233" t="n">
-        <v>-7.33428990531396</v>
+        <v>-7.27207522830263</v>
       </c>
       <c r="L233" t="n">
-        <v>-0.731228528033425</v>
+        <v>-0.730678860086241</v>
       </c>
       <c r="M233" t="n">
         <v>0</v>
@@ -23245,31 +23245,31 @@
         <v>0</v>
       </c>
       <c r="P233" t="n">
-        <v>-0.0791929877231321</v>
+        <v>-0.0791334979061532</v>
       </c>
       <c r="Q233" t="n">
-        <v>-0.0615128469594488</v>
+        <v>-0.0614666393184764</v>
       </c>
       <c r="R233" t="n">
-        <v>0.000203037980052656</v>
+        <v>0.000202885470332703</v>
       </c>
       <c r="S233" t="n">
-        <v>-0.00101686078217227</v>
+        <v>-0.00101609697752676</v>
       </c>
       <c r="T233" t="n">
-        <v>-0.000246217890141103</v>
+        <v>-0.000246032946242395</v>
       </c>
       <c r="U233" t="n">
-        <v>0.0225149866301508</v>
+        <v>0.0224980751381127</v>
       </c>
       <c r="V233" t="n">
-        <v>-0.000245537329284517</v>
+        <v>-0.000245352896528632</v>
       </c>
       <c r="W233" t="n">
-        <v>-5.99744240546112</v>
+        <v>-6.13623058137157</v>
       </c>
       <c r="X233" t="n">
-        <v>-0.958214967844601</v>
+        <v>-0.960290667058598</v>
       </c>
       <c r="Y233" t="e">
         <v>#NUM!</v>
@@ -23278,19 +23278,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA233" t="n">
-        <v>11.6727840385583</v>
+        <v>11.6708806076967</v>
       </c>
       <c r="AB233" t="n">
-        <v>-15.8716065544526</v>
+        <v>-15.9584096072099</v>
       </c>
       <c r="AC233" t="n">
-        <v>-2.2221443763655</v>
+        <v>-2.29942024135731</v>
       </c>
       <c r="AD233" t="n">
         <v>0</v>
       </c>
       <c r="AE233" t="n">
-        <v>-5.68257939950309</v>
+        <v>-5.6523802853871</v>
       </c>
     </row>
     <row r="234">
@@ -23310,25 +23310,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F234" t="n">
-        <v>3.8354944411779</v>
+        <v>3.83270248110967</v>
       </c>
       <c r="G234" t="n">
-        <v>2.07069044065283</v>
+        <v>2.07297019613939</v>
       </c>
       <c r="H234" t="n">
-        <v>0.227723792160673</v>
+        <v>0.227626951553901</v>
       </c>
       <c r="I234" t="n">
         <v>0</v>
       </c>
       <c r="J234" t="n">
-        <v>0.0783576813629675</v>
+        <v>0.0778468056340663</v>
       </c>
       <c r="K234" t="n">
-        <v>-7.36430820297969</v>
+        <v>-7.30174506424405</v>
       </c>
       <c r="L234" t="n">
-        <v>-0.728095181603661</v>
+        <v>-0.727547871106427</v>
       </c>
       <c r="M234" t="n">
         <v>0</v>
@@ -23340,31 +23340,31 @@
         <v>0</v>
       </c>
       <c r="P234" t="n">
-        <v>-0.0739572559884908</v>
+        <v>-0.0739016995602961</v>
       </c>
       <c r="Q234" t="n">
-        <v>-0.0589488506608058</v>
+        <v>-0.0589045691797218</v>
       </c>
       <c r="R234" t="n">
-        <v>0.000199348723298747</v>
+        <v>0.000199198984720084</v>
       </c>
       <c r="S234" t="n">
-        <v>-0.00102164807941644</v>
+        <v>-0.00102088067884133</v>
       </c>
       <c r="T234" t="n">
         <v>0</v>
       </c>
       <c r="U234" t="n">
-        <v>0.0207477666811622</v>
+        <v>0.0207321825573699</v>
       </c>
       <c r="V234" t="n">
-        <v>-0.000241053557252871</v>
+        <v>-0.000240872492470928</v>
       </c>
       <c r="W234" t="n">
-        <v>-5.97322864400373</v>
+        <v>-6.11139172378735</v>
       </c>
       <c r="X234" t="n">
-        <v>-0.95453096941944</v>
+        <v>-0.956649907224076</v>
       </c>
       <c r="Y234" t="e">
         <v>#NUM!</v>
@@ -23373,19 +23373,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA234" t="n">
-        <v>6.1069989763434</v>
+        <v>6.10582419383171</v>
       </c>
       <c r="AB234" t="n">
-        <v>-15.8617508994999</v>
+        <v>-15.9475906684427</v>
       </c>
       <c r="AC234" t="n">
-        <v>-8.73387771295107</v>
+        <v>-8.81508529266362</v>
       </c>
       <c r="AD234" t="n">
         <v>0</v>
       </c>
       <c r="AE234" t="n">
-        <v>-5.49302496854176</v>
+        <v>-5.47602332305971</v>
       </c>
     </row>
     <row r="235">
@@ -23405,25 +23405,25 @@
         <v>#NUM!</v>
       </c>
       <c r="F235" t="n">
-        <v>3.79055198273087</v>
+        <v>3.78779286057467</v>
       </c>
       <c r="G235" t="n">
-        <v>2.04898897475753</v>
+        <v>2.05124387182488</v>
       </c>
       <c r="H235" t="n">
-        <v>0.01200446971962</v>
+        <v>0.0120689115598191</v>
       </c>
       <c r="I235" t="n">
         <v>0</v>
       </c>
       <c r="J235" t="n">
-        <v>0.00577502922181358</v>
+        <v>0.00532369704549221</v>
       </c>
       <c r="K235" t="n">
-        <v>-7.26415941384648</v>
+        <v>-7.20285597133906</v>
       </c>
       <c r="L235" t="n">
-        <v>-0.723925351762704</v>
+        <v>-0.723381177657079</v>
       </c>
       <c r="M235" t="n">
         <v>0</v>
@@ -23435,31 +23435,31 @@
         <v>0</v>
       </c>
       <c r="P235" t="n">
-        <v>-0.069109569306645</v>
+        <v>-0.0690576546997014</v>
       </c>
       <c r="Q235" t="n">
-        <v>-0.0569848727572219</v>
+        <v>-0.0569420666707914</v>
       </c>
       <c r="R235" t="n">
-        <v>0.000195436411083312</v>
+        <v>0.000195289611156879</v>
       </c>
       <c r="S235" t="n">
-        <v>-0.000602707063401036</v>
+        <v>-0.000602254346317164</v>
       </c>
       <c r="T235" t="n">
         <v>0</v>
       </c>
       <c r="U235" t="n">
-        <v>0.0193266366341969</v>
+        <v>0.0193121199327352</v>
       </c>
       <c r="V235" t="n">
-        <v>-0.000236284647387811</v>
+        <v>-0.000236107164707188</v>
       </c>
       <c r="W235" t="n">
-        <v>-5.94178815237639</v>
+        <v>-6.07917906809492</v>
       </c>
       <c r="X235" t="n">
-        <v>-0.948345967006404</v>
+        <v>-0.950463080727114</v>
       </c>
       <c r="Y235" t="e">
         <v>#NUM!</v>
@@ -23468,19 +23468,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA235" t="n">
-        <v>5.77220772832667</v>
+        <v>5.77125755985333</v>
       </c>
       <c r="AB235" t="n">
-        <v>-15.7010578275158</v>
+        <v>-15.7872838859379</v>
       </c>
       <c r="AC235" t="n">
-        <v>-8.97318656589395</v>
+        <v>-9.0548244784642</v>
       </c>
       <c r="AD235" t="n">
         <v>0</v>
       </c>
       <c r="AE235" t="n">
-        <v>-5.33326240807133</v>
+        <v>-5.32487452640337</v>
       </c>
     </row>
     <row r="236">
@@ -23500,19 +23500,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F236" t="n">
-        <v>3.75364946940031</v>
+        <v>3.7509173295018</v>
       </c>
       <c r="G236" t="n">
-        <v>2.02982193615988</v>
+        <v>2.03205397794514</v>
       </c>
       <c r="H236" t="n">
-        <v>0.068441052443647</v>
+        <v>0.0693672466923897</v>
       </c>
       <c r="I236" t="n">
         <v>0</v>
       </c>
       <c r="J236" t="n">
-        <v>0.0753030343302221</v>
+        <v>0.0694199262577765</v>
       </c>
       <c r="K236" t="n">
         <v>0</v>
@@ -23530,25 +23530,25 @@
         <v>0</v>
       </c>
       <c r="P236" t="n">
-        <v>-0.0409446021188461</v>
+        <v>-0.0409138457282762</v>
       </c>
       <c r="Q236" t="n">
-        <v>-0.0494861451310024</v>
+        <v>-0.0494489722547452</v>
       </c>
       <c r="R236" t="n">
-        <v>0.000191969851177877</v>
+        <v>0.000191825655152041</v>
       </c>
       <c r="S236" t="n">
-        <v>-0.000601205191249771</v>
+        <v>-0.000600753602245456</v>
       </c>
       <c r="T236" t="n">
         <v>0</v>
       </c>
       <c r="U236" t="n">
-        <v>0.0123050377594143</v>
+        <v>0.0122957950823846</v>
       </c>
       <c r="V236" t="n">
-        <v>-0.0000794381856996428</v>
+        <v>-0.0000793785166235029</v>
       </c>
       <c r="W236" t="n">
         <v>0</v>
@@ -23563,19 +23563,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA236" t="n">
-        <v>5.83603232485594</v>
+        <v>5.83079879699938</v>
       </c>
       <c r="AB236" t="n">
-        <v>-0.0786245472818299</v>
+        <v>-0.0785654845186124</v>
       </c>
       <c r="AC236" t="n">
-        <v>5.76236368088285</v>
+        <v>5.75718403584444</v>
       </c>
       <c r="AD236" t="n">
         <v>0</v>
       </c>
       <c r="AE236" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="237">
@@ -23595,19 +23595,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F237" t="n">
-        <v>3.71308723677001</v>
+        <v>3.71038474375257</v>
       </c>
       <c r="G237" t="n">
-        <v>2.00987654386104</v>
+        <v>2.01208580884599</v>
       </c>
       <c r="H237" t="n">
-        <v>0.168761337795088</v>
+        <v>0.169587361865345</v>
       </c>
       <c r="I237" t="n">
         <v>0</v>
       </c>
       <c r="J237" t="n">
-        <v>0.0738623383780963</v>
+        <v>0.0680917442067688</v>
       </c>
       <c r="K237" t="n">
         <v>0</v>
@@ -23625,25 +23625,25 @@
         <v>0</v>
       </c>
       <c r="P237" t="n">
-        <v>-0.0221805559616482</v>
+        <v>-0.0221638948981404</v>
       </c>
       <c r="Q237" t="n">
-        <v>-0.0496523719061936</v>
+        <v>-0.0496150741585499</v>
       </c>
       <c r="R237" t="n">
-        <v>0.00044324525510416</v>
+        <v>0.000442912316409957</v>
       </c>
       <c r="S237" t="n">
-        <v>-0.000601412785644412</v>
+        <v>-0.000600961040748862</v>
       </c>
       <c r="T237" t="n">
         <v>0</v>
       </c>
       <c r="U237" t="n">
-        <v>0.0067906511762143</v>
+        <v>0.00678555048859803</v>
       </c>
       <c r="V237" t="n">
-        <v>-0.0000779406515372065</v>
+        <v>-0.0000778821072833646</v>
       </c>
       <c r="W237" t="n">
         <v>0</v>
@@ -23658,19 +23658,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA237" t="n">
-        <v>5.87013291190953</v>
+        <v>5.86491912121042</v>
       </c>
       <c r="AB237" t="n">
-        <v>-0.0652850983851142</v>
+        <v>-0.0652360568930802</v>
       </c>
       <c r="AC237" t="n">
-        <v>5.80898554444588</v>
+        <v>5.80381650626255</v>
       </c>
       <c r="AD237" t="n">
         <v>0</v>
       </c>
       <c r="AE237" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="238">
@@ -23690,19 +23690,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F238" t="n">
-        <v>3.74715450723628</v>
+        <v>3.74442604102605</v>
       </c>
       <c r="G238" t="n">
-        <v>1.992435833953</v>
+        <v>1.99462519601962</v>
       </c>
       <c r="H238" t="n">
-        <v>0.164755970851461</v>
+        <v>0.165562405957367</v>
       </c>
       <c r="I238" t="n">
         <v>0</v>
       </c>
       <c r="J238" t="n">
-        <v>0.0726139863270012</v>
+        <v>0.0669408838908742</v>
       </c>
       <c r="K238" t="n">
         <v>0</v>
@@ -23720,25 +23720,25 @@
         <v>0</v>
       </c>
       <c r="P238" t="n">
-        <v>-0.0223716348361572</v>
+        <v>-0.0223548302397794</v>
       </c>
       <c r="Q238" t="n">
-        <v>-0.0494335661497027</v>
+        <v>-0.0493964327750621</v>
       </c>
       <c r="R238" t="n">
         <v>0</v>
       </c>
       <c r="S238" t="n">
-        <v>-0.000502434175721073</v>
+        <v>-0.000502056777676855</v>
       </c>
       <c r="T238" t="n">
         <v>0</v>
       </c>
       <c r="U238" t="n">
-        <v>0.00666686795572179</v>
+        <v>0.00666186024520528</v>
       </c>
       <c r="V238" t="n">
-        <v>-0.0000765206319916611</v>
+        <v>-0.0000764631543575585</v>
       </c>
       <c r="W238" t="n">
         <v>0</v>
@@ -23753,19 +23753,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA238" t="n">
-        <v>5.88188411620007</v>
+        <v>5.87669808695704</v>
       </c>
       <c r="AB238" t="n">
-        <v>-0.0657243795167567</v>
+        <v>-0.0656750080235024</v>
       </c>
       <c r="AC238" t="n">
-        <v>5.82032792449831</v>
+        <v>5.81518697355911</v>
       </c>
       <c r="AD238" t="n">
         <v>0</v>
       </c>
       <c r="AE238" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="239">
@@ -23785,19 +23785,19 @@
         <v>#NUM!</v>
       </c>
       <c r="F239" t="n">
-        <v>3.70000008665802</v>
+        <v>3.69730589975057</v>
       </c>
       <c r="G239" t="n">
-        <v>1.97243691333279</v>
+        <v>1.97460288374637</v>
       </c>
       <c r="H239" t="n">
-        <v>0.160731989143741</v>
+        <v>0.161518742923104</v>
       </c>
       <c r="I239" t="n">
         <v>0</v>
       </c>
       <c r="J239" t="n">
-        <v>0.0713928120938873</v>
+        <v>0.0658150811957974</v>
       </c>
       <c r="K239" t="n">
         <v>0</v>
@@ -23815,25 +23815,25 @@
         <v>0</v>
       </c>
       <c r="P239" t="n">
-        <v>-0.0179725615943227</v>
+        <v>-0.0179590614513112</v>
       </c>
       <c r="Q239" t="n">
-        <v>-0.0498288393681295</v>
+        <v>-0.0497914090595142</v>
       </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
       <c r="S239" t="n">
-        <v>-0.000396826988864878</v>
+        <v>-0.000396528916466871</v>
       </c>
       <c r="T239" t="n">
         <v>0</v>
       </c>
       <c r="U239" t="n">
-        <v>0.0052433347696283</v>
+        <v>0.00523939631734106</v>
       </c>
       <c r="V239" t="n">
-        <v>-0.0000750771485229341</v>
+        <v>-0.0000750207551048551</v>
       </c>
       <c r="W239" t="n">
         <v>0</v>
@@ -23848,19 +23848,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA239" t="n">
-        <v>5.81187607108815</v>
+        <v>5.80677012396023</v>
       </c>
       <c r="AB239" t="n">
-        <v>-0.0630360401465371</v>
+        <v>-0.0629886882405232</v>
       </c>
       <c r="AC239" t="n">
-        <v>5.7527862100638</v>
+        <v>5.74772356308745</v>
       </c>
       <c r="AD239" t="n">
         <v>0</v>
       </c>
       <c r="AE239" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="240">
@@ -23886,13 +23886,13 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>0.156616650878038</v>
+        <v>0.157383275776311</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
       </c>
       <c r="J240" t="n">
-        <v>0.0699124281168817</v>
+        <v>0.0644503169810106</v>
       </c>
       <c r="K240" t="n">
         <v>0</v>
@@ -23913,13 +23913,13 @@
         <v>0</v>
       </c>
       <c r="Q240" t="n">
-        <v>-0.039504361764444</v>
+        <v>-0.0394746872873064</v>
       </c>
       <c r="R240" t="n">
         <v>0</v>
       </c>
       <c r="S240" t="n">
-        <v>-0.000293753051528703</v>
+        <v>-0.000293532402101051</v>
       </c>
       <c r="T240" t="n">
         <v>0</v>
@@ -23943,19 +23943,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA240" t="n">
-        <v>0.226412277898501</v>
+        <v>0.221725325299258</v>
       </c>
       <c r="AB240" t="n">
-        <v>-0.0397982385464291</v>
+        <v>-0.0397683433088845</v>
       </c>
       <c r="AC240" t="n">
-        <v>0.186710153598348</v>
+        <v>0.182051092135654</v>
       </c>
       <c r="AD240" t="n">
         <v>0</v>
       </c>
       <c r="AE240" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="241">
@@ -23981,13 +23981,13 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>0.152724102426152</v>
+        <v>0.153471687274904</v>
       </c>
       <c r="I241" t="n">
         <v>0</v>
       </c>
       <c r="J241" t="n">
-        <v>0.0686656419318574</v>
+        <v>0.0633009062598385</v>
       </c>
       <c r="K241" t="n">
         <v>0</v>
@@ -24008,13 +24008,13 @@
         <v>0</v>
       </c>
       <c r="Q241" t="n">
-        <v>-0.0392079562284777</v>
+        <v>-0.0391785044114907</v>
       </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
       <c r="S241" t="n">
-        <v>-0.000193846867566195</v>
+        <v>-0.000193701261535458</v>
       </c>
       <c r="T241" t="n">
         <v>0</v>
@@ -24038,19 +24038,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA241" t="n">
-        <v>0.221277918535408</v>
+        <v>0.216668937881747</v>
       </c>
       <c r="AB241" t="n">
-        <v>-0.0394018841038229</v>
+        <v>-0.0393722866082596</v>
       </c>
       <c r="AC241" t="n">
-        <v>0.181968999492182</v>
+        <v>0.177387666015992</v>
       </c>
       <c r="AD241" t="n">
         <v>0</v>
       </c>
       <c r="AE241" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="242">
@@ -24076,13 +24076,13 @@
         <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>0.152850030377927</v>
+        <v>0.153576654484618</v>
       </c>
       <c r="I242" t="n">
         <v>0</v>
       </c>
       <c r="J242" t="n">
-        <v>0.0672866753263317</v>
+        <v>0.0620296383491121</v>
       </c>
       <c r="K242" t="n">
         <v>0</v>
@@ -24103,13 +24103,13 @@
         <v>0</v>
       </c>
       <c r="Q242" t="n">
-        <v>-0.0382719464676964</v>
+        <v>-0.0382431977818835</v>
       </c>
       <c r="R242" t="n">
         <v>0</v>
       </c>
       <c r="S242" t="n">
-        <v>-0.0000967992287459444</v>
+        <v>-0.0000967265190715846</v>
       </c>
       <c r="T242" t="n">
         <v>0</v>
@@ -24133,19 +24133,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA242" t="n">
-        <v>0.220027183848495</v>
+        <v>0.215504787122681</v>
       </c>
       <c r="AB242" t="n">
-        <v>-0.0383687851293907</v>
+        <v>-0.0383399636985014</v>
       </c>
       <c r="AC242" t="n">
-        <v>0.181748292795029</v>
+        <v>0.177252856350163</v>
       </c>
       <c r="AD242" t="n">
         <v>0</v>
       </c>
       <c r="AE242" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="243">
@@ -24171,13 +24171,13 @@
         <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>0.149226791444266</v>
+        <v>0.149936208305387</v>
       </c>
       <c r="I243" t="n">
         <v>0</v>
       </c>
       <c r="J243" t="n">
-        <v>0.0658542310726151</v>
+        <v>0.0607090696555701</v>
       </c>
       <c r="K243" t="n">
         <v>0</v>
@@ -24198,7 +24198,7 @@
         <v>0</v>
       </c>
       <c r="Q243" t="n">
-        <v>-0.0375957467010318</v>
+        <v>-0.0375675059774387</v>
       </c>
       <c r="R243" t="n">
         <v>0</v>
@@ -24228,19 +24228,19 @@
         <v>#NUM!</v>
       </c>
       <c r="AA243" t="n">
-        <v>0.2149766183383</v>
+        <v>0.210548515387925</v>
       </c>
       <c r="AB243" t="n">
-        <v>-0.0375957467010318</v>
+        <v>-0.0375675059774387</v>
       </c>
       <c r="AC243" t="n">
-        <v>0.177466731163623</v>
+        <v>0.173065087533157</v>
       </c>
       <c r="AD243" t="n">
         <v>0</v>
       </c>
       <c r="AE243" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="244">
@@ -24293,7 +24293,7 @@
         <v>0</v>
       </c>
       <c r="Q244" t="n">
-        <v>-0.0125990318901856</v>
+        <v>-0.0125895681428152</v>
       </c>
       <c r="R244" t="n">
         <v>0</v>
@@ -24326,16 +24326,16 @@
         <v>0</v>
       </c>
       <c r="AB244" t="n">
-        <v>-0.0125990318901856</v>
+        <v>-0.0125895681428152</v>
       </c>
       <c r="AC244" t="n">
-        <v>-0.0125990318901856</v>
+        <v>-0.0125895681428152</v>
       </c>
       <c r="AD244" t="n">
         <v>0</v>
       </c>
       <c r="AE244" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="245">
@@ -24388,7 +24388,7 @@
         <v>0</v>
       </c>
       <c r="Q245" t="n">
-        <v>-0.0123700239874886</v>
+        <v>-0.0123607322614311</v>
       </c>
       <c r="R245" t="n">
         <v>0</v>
@@ -24421,16 +24421,16 @@
         <v>0</v>
       </c>
       <c r="AB245" t="n">
-        <v>-0.0123700239874886</v>
+        <v>-0.0123607322614311</v>
       </c>
       <c r="AC245" t="n">
-        <v>-0.0123700239874886</v>
+        <v>-0.0123607322614311</v>
       </c>
       <c r="AD245" t="n">
         <v>0</v>
       </c>
       <c r="AE245" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="246">
@@ -24483,7 +24483,7 @@
         <v>0</v>
       </c>
       <c r="Q246" t="n">
-        <v>-0.0121343766564271</v>
+        <v>-0.0121252619388607</v>
       </c>
       <c r="R246" t="n">
         <v>0</v>
@@ -24516,16 +24516,16 @@
         <v>0</v>
       </c>
       <c r="AB246" t="n">
-        <v>-0.0121343766564271</v>
+        <v>-0.0121252619388607</v>
       </c>
       <c r="AC246" t="n">
-        <v>-0.0121343766564271</v>
+        <v>-0.0121252619388607</v>
       </c>
       <c r="AD246" t="n">
         <v>0</v>
       </c>
       <c r="AE246" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="247">
@@ -24578,7 +24578,7 @@
         <v>0</v>
       </c>
       <c r="Q247" t="n">
-        <v>-0.0119112091449515</v>
+        <v>-0.0119022620615163</v>
       </c>
       <c r="R247" t="n">
         <v>0</v>
@@ -24611,16 +24611,16 @@
         <v>0</v>
       </c>
       <c r="AB247" t="n">
-        <v>-0.0119112091449515</v>
+        <v>-0.0119022620615163</v>
       </c>
       <c r="AC247" t="n">
-        <v>-0.0119112091449515</v>
+        <v>-0.0119022620615163</v>
       </c>
       <c r="AD247" t="n">
         <v>0</v>
       </c>
       <c r="AE247" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="248">
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="AE248" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="249">
@@ -24810,7 +24810,7 @@
         <v>0</v>
       </c>
       <c r="AE249" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="250">
@@ -24905,7 +24905,7 @@
         <v>0</v>
       </c>
       <c r="AE250" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="251">
@@ -25000,7 +25000,7 @@
         <v>0</v>
       </c>
       <c r="AE251" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="252">
@@ -25095,7 +25095,7 @@
         <v>0</v>
       </c>
       <c r="AE252" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="253">
@@ -25190,7 +25190,7 @@
         <v>0</v>
       </c>
       <c r="AE253" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="254">
@@ -25285,7 +25285,7 @@
         <v>0</v>
       </c>
       <c r="AE254" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="255">
@@ -25380,7 +25380,7 @@
         <v>0</v>
       </c>
       <c r="AE255" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="256">
@@ -25475,7 +25475,7 @@
         <v>0</v>
       </c>
       <c r="AE256" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="257">
@@ -25570,7 +25570,7 @@
         <v>0</v>
       </c>
       <c r="AE257" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="258">
@@ -25665,7 +25665,7 @@
         <v>0</v>
       </c>
       <c r="AE258" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="259">
@@ -25760,7 +25760,7 @@
         <v>0</v>
       </c>
       <c r="AE259" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
     <row r="260">
@@ -25855,7 +25855,7 @@
         <v>0</v>
       </c>
       <c r="AE260" t="n">
-        <v>0.00000000000000177635683940025</v>
+        <v>-0.000000000000000888178419700125</v>
       </c>
     </row>
   </sheetData>
